--- a/Results/TestCases/XLSX/recruitment_TestCases.xlsx
+++ b/Results/TestCases/XLSX/recruitment_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="71">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -72,13 +72,16 @@
     <t>High</t>
   </si>
   <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>TC_REC_02</t>
+  </si>
+  <si>
+    <t>Search candidate records</t>
+  </si>
+  <si>
     <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>TC_REC_02</t>
-  </si>
-  <si>
-    <t>Search candidate records</t>
   </si>
   <si>
     <t>TC_REC_03</t>
@@ -229,7 +232,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -249,12 +252,18 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFA51D24"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF5A6268"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -264,6 +273,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF7919"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -310,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -319,6 +333,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -774,13 +791,13 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>19</v>
+      <c r="K3" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -789,13 +806,13 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -809,13 +826,13 @@
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
+      <c r="K4" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -824,13 +841,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -842,15 +859,15 @@
         <v>17</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -859,13 +876,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -877,15 +894,15 @@
         <v>17</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -894,13 +911,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -912,15 +929,15 @@
         <v>17</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -929,13 +946,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -947,15 +964,15 @@
         <v>17</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -964,13 +981,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -982,15 +999,15 @@
         <v>17</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -999,13 +1016,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -1017,15 +1034,15 @@
         <v>17</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1034,13 +1051,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1052,15 +1069,15 @@
         <v>17</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1069,14 +1086,14 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
@@ -1087,30 +1104,30 @@
         <v>17</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1122,15 +1139,15 @@
         <v>17</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1139,13 +1156,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1157,15 +1174,15 @@
         <v>17</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1174,13 +1191,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1192,15 +1209,15 @@
         <v>17</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1209,13 +1226,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1227,15 +1244,15 @@
         <v>17</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1244,13 +1261,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -1262,15 +1279,15 @@
         <v>17</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1279,13 +1296,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -1297,15 +1314,15 @@
         <v>17</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1314,13 +1331,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -1332,15 +1349,15 @@
         <v>17</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1349,13 +1366,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1367,15 +1384,15 @@
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1384,13 +1401,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1402,15 +1419,15 @@
         <v>17</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1419,13 +1436,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1437,15 +1454,15 @@
         <v>17</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1454,13 +1471,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1472,15 +1489,15 @@
         <v>17</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1489,13 +1506,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1507,15 +1524,15 @@
         <v>17</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1524,13 +1541,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1542,15 +1559,15 @@
         <v>17</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1559,13 +1576,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1577,10 +1594,10 @@
         <v>17</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Results/TestCases/XLSX/recruitment_TestCases.xlsx
+++ b/Results/TestCases/XLSX/recruitment_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="101">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,168 +58,265 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The user is logged in to OrangeHRM with valid credentials and the Dashboard has loaded. The user has navigated to the 'Recruitment' module.</t>
+  </si>
+  <si>
+    <t>1. Perform the actions described in the test title</t>
+  </si>
+  <si>
+    <t>- The 'Application Stage' element should be visible</t>
   </si>
   <si>
     <t>High</t>
   </si>
   <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>TC_REC_02</t>
+  </si>
+  <si>
+    <t>Search candidate records</t>
+  </si>
+  <si>
+    <t>- The exists should equal 'true'</t>
+  </si>
+  <si>
+    <t>TC_REC_03</t>
+  </si>
+  <si>
+    <t>Verify Recruitment page has Add button visible</t>
+  </si>
+  <si>
+    <t>- The add button should be visible</t>
+  </si>
+  <si>
+    <t>TC_REC_04</t>
+  </si>
+  <si>
+    <t>Verify Candidates tab is functional</t>
+  </si>
+  <si>
+    <t>1. Click the candidates tab</t>
+  </si>
+  <si>
+    <t>- The Search button should be visible</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TC_REC_05</t>
+  </si>
+  <si>
+    <t>Verify top navigation contains Vacancies tab</t>
+  </si>
+  <si>
+    <t>- The 'Vacancies' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_REC_06</t>
+  </si>
+  <si>
+    <t>Verify job title dropdown filter is visible</t>
+  </si>
+  <si>
+    <t>- The 'Job Title' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_REC_07</t>
+  </si>
+  <si>
+    <t>Verify vacancy dropdown filter is visible</t>
+  </si>
+  <si>
+    <t>- The 'Vacancy' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_REC_08</t>
+  </si>
+  <si>
+    <t>Verify hiring manager dropdown filter is visible</t>
+  </si>
+  <si>
+    <t>- The 'Hiring Manager' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_REC_09</t>
+  </si>
+  <si>
+    <t>Verify status dropdown filter is visible</t>
+  </si>
+  <si>
+    <t>- The 'Status' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_REC_10</t>
+  </si>
+  <si>
+    <t>Verify method of application dropdown filter is visible</t>
+  </si>
+  <si>
+    <t>- The 'Method of Application' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_REC_11</t>
+  </si>
+  <si>
+    <t>Verify validation error on empty First Name input</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click the add button
+2. Click the Save button</t>
+  </si>
+  <si>
+    <t>- The err should display the text 'Required'</t>
+  </si>
+  <si>
     <t>FAILED</t>
   </si>
   <si>
-    <t>TC_REC_02</t>
-  </si>
-  <si>
-    <t>Search candidate records</t>
+    <t>TC_REC_12</t>
+  </si>
+  <si>
+    <t>Verify validation error on empty Last Name input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click the add button
+2. Enter 'Soph' into the First Name field
+3. Click the Save button</t>
   </si>
   <si>
     <t>SKIPPED</t>
   </si>
   <si>
-    <t>TC_REC_03</t>
-  </si>
-  <si>
-    <t>Verify Recruitment page has Add button visible</t>
-  </si>
-  <si>
-    <t>TC_REC_04</t>
-  </si>
-  <si>
-    <t>Verify Candidates tab is functional</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>TC_REC_05</t>
-  </si>
-  <si>
-    <t>Verify top navigation contains Vacancies tab</t>
-  </si>
-  <si>
-    <t>TC_REC_06</t>
-  </si>
-  <si>
-    <t>Verify job title dropdown filter is visible</t>
-  </si>
-  <si>
-    <t>TC_REC_07</t>
-  </si>
-  <si>
-    <t>Verify vacancy dropdown filter is visible</t>
-  </si>
-  <si>
-    <t>TC_REC_08</t>
-  </si>
-  <si>
-    <t>Verify hiring manager dropdown filter is visible</t>
-  </si>
-  <si>
-    <t>TC_REC_09</t>
-  </si>
-  <si>
-    <t>Verify status dropdown filter is visible</t>
-  </si>
-  <si>
-    <t>TC_REC_10</t>
-  </si>
-  <si>
-    <t>Verify method of application dropdown filter is visible</t>
-  </si>
-  <si>
-    <t>TC_REC_11</t>
-  </si>
-  <si>
-    <t>Verify validation error on empty First Name input</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>TC_REC_12</t>
-  </si>
-  <si>
-    <t>Verify validation error on empty Last Name input</t>
-  </si>
-  <si>
     <t>TC_REC_13</t>
   </si>
   <si>
     <t>Verify validation error on empty Email input</t>
   </si>
   <si>
+    <t>- The 'Email' element should display the text 'Required'</t>
+  </si>
+  <si>
     <t>TC_REC_14</t>
   </si>
   <si>
     <t>Verify validation error on invalid Email format</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the add button
+2. Enter 'invalidemailformat' into the email input
+3. Click the Save button</t>
+  </si>
+  <si>
+    <t>- The 'Email' element should display the text 'Expected format: admin@example.com'</t>
+  </si>
+  <si>
     <t>TC_REC_15</t>
   </si>
   <si>
     <t>Verify Cancel button on Add Candidate form returns to candidates page</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the add button
+2. Click the oxd button  ghost element</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain '/recruitment/viewCandidates'</t>
+  </si>
+  <si>
     <t>TC_REC_16</t>
   </si>
   <si>
     <t>Verify Reset button clears Candidate Name input</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the candidates tab
+2. Click the option
+3. Click the 'Reset' element</t>
+  </si>
+  <si>
+    <t>- The search candidate name input should have the value ''</t>
+  </si>
+  <si>
     <t>TC_REC_17</t>
   </si>
   <si>
     <t>Verify Recruitment header breadcrumb displays Recruitment / Candidates</t>
   </si>
   <si>
+    <t>- The breadcrumb should contain the text 'Recruitment'</t>
+  </si>
+  <si>
     <t>TC_REC_18</t>
   </si>
   <si>
     <t>Verify table checkboxes exist for recruitment rows</t>
   </si>
   <si>
+    <t>- The check should be present</t>
+  </si>
+  <si>
     <t>TC_REC_19</t>
   </si>
   <si>
     <t>Verify date of application filter inputs are visible</t>
   </si>
   <si>
+    <t xml:space="preserve">- The 'From Date' element should be visible
+- The 'To Date' element should be visible</t>
+  </si>
+  <si>
     <t>TC_REC_20</t>
   </si>
   <si>
     <t>Verify Keywords input is functional</t>
   </si>
   <si>
+    <t>- The 'Keywords' element should be visible</t>
+  </si>
+  <si>
     <t>TC_REC_21</t>
   </si>
   <si>
     <t>Verify select all checkbox is in the header</t>
   </si>
   <si>
+    <t>- The header check should be visible</t>
+  </si>
+  <si>
     <t>TC_REC_22</t>
   </si>
   <si>
     <t>Verify records text is visible above the table</t>
   </si>
   <si>
+    <t>- The records should be visible</t>
+  </si>
+  <si>
     <t>TC_REC_23</t>
   </si>
   <si>
     <t>Verify file upload field accepts doc/docx/pdf file types</t>
   </si>
   <si>
+    <t>1. Click the add button</t>
+  </si>
+  <si>
+    <t>- The resume input should be present in the DOM</t>
+  </si>
+  <si>
     <t>TC_REC_24</t>
   </si>
   <si>
     <t>Verify consent checkbox is visible in Add Candidate form</t>
+  </si>
+  <si>
+    <t>- The checkbox element should be present</t>
   </si>
   <si>
     <t>TC_REC_25</t>
@@ -232,7 +329,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -252,6 +349,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF107C41"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFA51D24"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
@@ -263,7 +366,7 @@
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -273,6 +376,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF7919"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1E7DD"/>
       </patternFill>
     </fill>
     <fill>
@@ -324,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -336,6 +444,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -786,13 +897,13 @@
         <v>16</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>22</v>
+      <c r="K3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -821,18 +932,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>22</v>
+      <c r="K4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -841,33 +952,33 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -876,13 +987,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -891,18 +1002,18 @@
         <v>16</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -911,13 +1022,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -926,18 +1037,18 @@
         <v>16</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -946,13 +1057,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -961,18 +1072,18 @@
         <v>16</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -981,13 +1092,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -996,18 +1107,18 @@
         <v>16</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1016,13 +1127,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -1031,18 +1142,18 @@
         <v>16</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1051,13 +1162,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1066,18 +1177,18 @@
         <v>16</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1086,33 +1197,33 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1121,33 +1232,33 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1156,33 +1267,33 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1191,33 +1302,33 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1226,33 +1337,33 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1261,33 +1372,33 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1296,13 +1407,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -1311,18 +1422,18 @@
         <v>16</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1331,13 +1442,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -1346,18 +1457,18 @@
         <v>16</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1366,13 +1477,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1381,18 +1492,18 @@
         <v>16</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1401,13 +1512,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1416,18 +1527,18 @@
         <v>16</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1436,13 +1547,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1451,18 +1562,18 @@
         <v>16</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1471,13 +1582,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1486,18 +1597,18 @@
         <v>16</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1506,33 +1617,33 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1541,33 +1652,33 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1576,28 +1687,28 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Results/TestCases/XLSX/recruitment_TestCases.xlsx
+++ b/Results/TestCases/XLSX/recruitment_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="100">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -70,7 +70,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>PASSED</t>
+    <t>FAILED</t>
   </si>
   <si>
     <t>TC_REC_02</t>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>- The exists should equal 'true'</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
   </si>
   <si>
     <t>TC_REC_03</t>
@@ -174,9 +177,6 @@
   </si>
   <si>
     <t>- The err should display the text 'Required'</t>
-  </si>
-  <si>
-    <t>FAILED</t>
   </si>
   <si>
     <t>TC_REC_12</t>
@@ -190,9 +190,6 @@
 3. Click the Save button</t>
   </si>
   <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
     <t>TC_REC_13</t>
   </si>
   <si>
@@ -267,8 +264,8 @@
     <t>Verify date of application filter inputs are visible</t>
   </si>
   <si>
-    <t xml:space="preserve">- The 'From Date' element should be visible
-- The 'To Date' element should be visible</t>
+    <t xml:space="preserve">- The 'Date of Application' element should be visible
+- The 'To' field should be visible</t>
   </si>
   <si>
     <t>TC_REC_20</t>
@@ -329,7 +326,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -349,12 +346,6 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF107C41"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FFA51D24"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
@@ -366,7 +357,7 @@
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -376,11 +367,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF7919"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1E7DD"/>
       </patternFill>
     </fill>
     <fill>
@@ -432,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -444,9 +430,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -902,13 +885,13 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>19</v>
+      <c r="K3" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -917,13 +900,13 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -932,18 +915,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
+      <c r="K4" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -952,33 +935,33 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -987,13 +970,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -1002,18 +985,18 @@
         <v>16</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -1022,13 +1005,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -1037,18 +1020,18 @@
         <v>16</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -1057,13 +1040,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -1072,18 +1055,18 @@
         <v>16</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -1092,13 +1075,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -1107,18 +1090,18 @@
         <v>16</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1127,13 +1110,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -1142,18 +1125,18 @@
         <v>16</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1162,13 +1145,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1177,18 +1160,18 @@
         <v>16</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1197,28 +1180,28 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1235,7 +1218,7 @@
         <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>56</v>
@@ -1247,173 +1230,173 @@
         <v>57</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="J14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="J16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -1422,33 +1405,33 @@
         <v>16</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -1457,33 +1440,33 @@
         <v>16</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1492,33 +1475,33 @@
         <v>16</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1527,33 +1510,33 @@
         <v>16</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1562,33 +1545,33 @@
         <v>16</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1597,118 +1580,118 @@
         <v>16</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="J24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
